--- a/artfynd/A 30478-2025 artfynd.xlsx
+++ b/artfynd/A 30478-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136151704</v>
       </c>
       <c r="B2" t="n">
-        <v>100612</v>
+        <v>100615</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30478-2025 artfynd.xlsx
+++ b/artfynd/A 30478-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136151704</v>
       </c>
       <c r="B2" t="n">
-        <v>100615</v>
+        <v>100616</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30478-2025 artfynd.xlsx
+++ b/artfynd/A 30478-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136151704</v>
       </c>
       <c r="B2" t="n">
-        <v>100616</v>
+        <v>100621</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30478-2025 artfynd.xlsx
+++ b/artfynd/A 30478-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136151704</v>
       </c>
       <c r="B2" t="n">
-        <v>100621</v>
+        <v>100623</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
